--- a/_106_Weapons.xlsx
+++ b/_106_Weapons.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8FF459-2411-495E-9E60-02EA3FAACCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB47FE2-9F26-4E73-AC08-66303C29EDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20550" yWindow="1760" windowWidth="21600" windowHeight="11330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -186,34 +186,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
